--- a/data/Example-data.xlsx
+++ b/data/Example-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\1、投稿\1.论文\2025-1基于特征预训练和嵌入注意力深度框架揭示空间竞争和相邻树种对杉木树冠分配的影响\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32D71CD-2643-4CF1-81DB-91CB9858C094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E602B97-6944-42DB-8014-0F51A3838015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,24 +37,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>TYPE</t>
-  </si>
-  <si>
-    <t>胸径</t>
-  </si>
-  <si>
-    <t>树高</t>
-  </si>
-  <si>
-    <t>枝下高</t>
-  </si>
-  <si>
-    <t>方向</t>
-  </si>
-  <si>
-    <t>总冠幅</t>
-  </si>
-  <si>
-    <t>单方向冠幅</t>
   </si>
   <si>
     <t>DIS1</t>
@@ -109,6 +91,30 @@
   </si>
   <si>
     <t>TYPE_nearest1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DBH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UBH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DIR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCW</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -499,76 +505,76 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
